--- a/docs/Fonde_2025.xlsx
+++ b/docs/Fonde_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\R_document\phd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F36F1A-D247-466E-96DA-C787EA24BE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2B1DE3-9040-4CB5-BA03-528241755391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3825" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>Diabetesforeningen</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Innovationsfonden</t>
   </si>
   <si>
-    <t>ROCKWOOL fonden</t>
-  </si>
-  <si>
-    <t>Velux fonden</t>
-  </si>
-  <si>
     <t>Frist</t>
   </si>
   <si>
@@ -86,21 +80,12 @@
     <t>Løn</t>
   </si>
   <si>
-    <t>02.09.2025</t>
-  </si>
-  <si>
     <t>midst 1 år</t>
   </si>
   <si>
     <t>300.000 EUR</t>
   </si>
   <si>
-    <t>20.06.2025</t>
-  </si>
-  <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>Prioritering</t>
   </si>
   <si>
@@ -119,18 +104,12 @@
     <t>29.04.2025</t>
   </si>
   <si>
-    <t>01.07.2025</t>
-  </si>
-  <si>
     <t>20.08.2025</t>
   </si>
   <si>
     <t>26.11.2025</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>19.06.2026</t>
   </si>
   <si>
@@ -162,6 +141,51 @@
   </si>
   <si>
     <t>4x årligt</t>
+  </si>
+  <si>
+    <t>Danske Fysioterapeuter</t>
+  </si>
+  <si>
+    <t>01.10.2026</t>
+  </si>
+  <si>
+    <t>40 - 100.000</t>
+  </si>
+  <si>
+    <t>Trygfonden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x årligt </t>
+  </si>
+  <si>
+    <t>Marts og september</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>https://tryghed.dk/sog-stotte</t>
+  </si>
+  <si>
+    <t>Tidligere støtte patientuddannelse</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>Helsefonden</t>
+  </si>
+  <si>
+    <t>https://helsefonden.dk/saadan-soeger-du-bevilling/</t>
+  </si>
+  <si>
+    <t>OBS minimum 5 millioner</t>
+  </si>
+  <si>
+    <t>01.07.2026</t>
+  </si>
+  <si>
+    <t>02.09.2026</t>
   </si>
 </sst>
 </file>
@@ -533,330 +557,328 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="15" customWidth="1"/>
     <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="F1" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E2" s="7">
         <v>2200000</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="8"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="7">
         <v>1100000</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="7">
-        <v>5000000</v>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5000000</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="11">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5000000</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="11">
-        <v>100000</v>
+        <v>16</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="E10" s="7">
+        <v>10000</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E13" s="3"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="15"/>
-      <c r="G14"/>
-      <c r="H14"/>
-    </row>
-    <row r="15" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
+      <c r="F12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" s="3">
+        <v>300000</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I22">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I20">
     <sortCondition descending="1" ref="F1"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="H6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H4" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C20" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H11" r:id="rId9" location="fundats+for+danske+fysioterapeuters+fond+for+forskning+uddannelse+og+praksisudvikling" xr:uid="{E662CC13-418E-4512-A61D-170E6C49EDFA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 

--- a/docs/Fonde_2025.xlsx
+++ b/docs/Fonde_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\R_document\phd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2B1DE3-9040-4CB5-BA03-528241755391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092ED1F-F9CC-4FE2-901C-DD1CE3602C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>Diabetesforeningen</t>
   </si>
@@ -149,9 +149,6 @@
     <t>01.10.2026</t>
   </si>
   <si>
-    <t>40 - 100.000</t>
-  </si>
-  <si>
     <t>Trygfonden</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>Tidligere støtte patientuddannelse</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Helsefonden</t>
   </si>
   <si>
@@ -186,6 +180,12 @@
   </si>
   <si>
     <t>02.09.2026</t>
+  </si>
+  <si>
+    <t>01.08.26</t>
+  </si>
+  <si>
+    <t>40.000 - 100.000 kr.</t>
   </si>
 </sst>
 </file>
@@ -195,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;kr.&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -231,8 +231,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -241,7 +249,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,23 +273,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -562,303 +595,282 @@
   <cols>
     <col min="1" max="1" width="49.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="15" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="19">
         <v>2200000</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="H2" s="13"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="20">
         <v>1100000</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="19">
         <v>5000000</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+    </row>
+    <row r="6" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="21">
         <v>100000</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="H9" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="17">
+        <v>10000</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="8" t="s">
+      <c r="F11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="13" t="s">
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="17">
+        <v>300000</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12"/>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12"/>
-      <c r="H12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" s="3">
-        <v>300000</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="H13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G13"/>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="14" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E14" s="17"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="16" t="s">
         <v>11</v>
       </c>
     </row>

--- a/docs/Fonde_2025.xlsx
+++ b/docs/Fonde_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\R_document\phd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092ED1F-F9CC-4FE2-901C-DD1CE3602C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B67C589-188F-4AAB-9990-BC99B102D3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>Diabetesforeningen</t>
   </si>
@@ -186,6 +186,15 @@
   </si>
   <si>
     <t>40.000 - 100.000 kr.</t>
+  </si>
+  <si>
+    <t>DFF klinisk forskning</t>
+  </si>
+  <si>
+    <t>Start juni</t>
+  </si>
+  <si>
+    <t>Det aftal</t>
   </si>
 </sst>
 </file>
@@ -863,8 +872,15 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E14" s="17"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
